--- a/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
@@ -5369,19 +5369,14 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Ing - Isb
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
+          <t>Mat - Bre/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
 1º e 2º tempos</t>
         </is>
       </c>
@@ -5466,8 +5461,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-6º e 7º tempos</t>
+          <t>Ing - Isb
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -5480,8 +5475,8 @@
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-2º ao 4º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -5542,20 +5537,20 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
+          <t>DaF - CBu-EFr-Eth
 3º e 4º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-EFr-Eth
-6º e 7º tempos</t>
+          <t>Bio - Ale
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-11º e 12º tempos</t>
+          <t>Qui - CAl/Fab
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -5619,20 +5614,20 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+2º ao 4º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -5775,21 +5770,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
+      <c r="E24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
         <is>
           <t>Bio - Ale
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G24" s="362" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-2º ao 4º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -5858,13 +5853,13 @@
       <c r="E27" s="78" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="inlineStr">
         <is>
-          <t>GL - CBu-EFr-Eth
-6º e 7º tempos</t>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G27" s="283" t="n"/>
@@ -5935,7 +5930,12 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="inlineStr">
         <is>
@@ -6110,21 +6110,21 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Hist - Wag
-11º e 12º tempos</t>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+2º ao 4º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
       <c r="E39" s="283" t="inlineStr">
         <is>
           <t>Ing - Isb
-5º e 6º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="283" t="n"/>
@@ -6245,14 +6245,14 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6307,17 +6307,17 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
+          <t>Mat - Bre/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="inlineStr">
         <is>
@@ -8590,16 +8590,21 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>Geo - Mar
-2º e 3º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
+          <t>Hist - JuLa
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
           <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -8679,19 +8684,19 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Ing - APa-PaH-Velo
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
@@ -8750,12 +8755,7 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -8826,17 +8826,17 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
+          <t>Mat - BrSa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 5º e 6º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
@@ -8903,13 +8903,13 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 3º e 4º tempos</t>
         </is>
       </c>
-      <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
@@ -8977,8 +8977,8 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º tempo</t>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
@@ -9051,12 +9051,7 @@
         <v/>
       </c>
       <c r="E27" s="78" t="n"/>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
@@ -9132,16 +9127,11 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Redação - Raf
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
-3º e 4º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -9310,15 +9300,20 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
+      <c r="E36" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+1º tempo</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-7º tempo</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -9384,16 +9379,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+7º tempo</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9441,13 +9441,13 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-7º tempo</t>
-        </is>
-      </c>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -9500,15 +9500,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="n"/>
+      <c r="E45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+7º tempo</t>
+        </is>
+      </c>
       <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -9557,12 +9562,7 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="n"/>
       <c r="F48" s="360" t="inlineStr">
         <is>
           <t>Port - Jana
@@ -10255,17 +10255,17 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>GL - Caro-EFr-Eth
+          <t>Hist - JuLa
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Port - Jana
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -10347,19 +10347,19 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Hist - JuLa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
           <t>Ing - APa-PaH-Velo
-5º e 6º tempos</t>
-        </is>
-      </c>
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10418,17 +10418,17 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Redação - Raf
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="n"/>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Port - Jana
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
@@ -10492,17 +10492,17 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
@@ -10571,18 +10571,18 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+          <t>Ing - APa-PaH-Velo
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Redação - Raf
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -10646,11 +10646,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-1º tempo</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="G24" s="79" t="n"/>
@@ -10796,14 +10801,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -10973,14 +10978,14 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Qui - Fab
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -11045,14 +11050,14 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Port - Jana
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -11102,8 +11107,8 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa-PaH-Velo
-5º e 6º tempos</t>
+          <t>Bio - Ale
+1º tempo</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
@@ -11161,17 +11166,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Qui - Fab
+2º tempo</t>
         </is>
       </c>
       <c r="H45" s="283" t="n"/>
@@ -11225,14 +11225,14 @@
       </c>
       <c r="E48" s="283" t="inlineStr">
         <is>
-          <t>Hist - JuLa
-6º e 7º tempos</t>
+          <t>Fis - VSi
+2º tempo</t>
         </is>
       </c>
       <c r="F48" s="360" t="inlineStr">
         <is>
           <t>DaF - Caro-SGa-EFr
-2º e 3º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="G48" s="283" t="n"/>
@@ -11921,19 +11921,19 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Fis - VSi
+          <t>Ing - APa
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>Bio - Lza
 6º e 7º tempos</t>
         </is>
       </c>
       <c r="G9" s="183" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
@@ -12018,19 +12018,24 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
+          <t>Fis - VSi
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-10º e 11º tempos</t>
+          <t>Qui - CAl
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+2º ao 4º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -12089,21 +12094,16 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ing - APa
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Hist - ALu
 5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -12166,17 +12166,17 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-8º ao 10º tempos</t>
+          <t>Geo - Mlo
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="inlineStr">
@@ -12253,7 +12253,7 @@
       <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Fis - VSi
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
@@ -12324,12 +12324,17 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
+      <c r="G24" s="362" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -12397,20 +12402,15 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+5º e 6º tempos</t>
+        </is>
+      </c>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -12477,14 +12477,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -12654,17 +12659,12 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
-5º e 6º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -12733,18 +12733,18 @@
       </c>
       <c r="E39" s="283" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
+          <t>Ing - APa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -12793,8 +12793,8 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
+          <t>Qui - CAl
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G42" s="283" t="n"/>
@@ -12852,20 +12852,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E45" s="283" t="n"/>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
-      <c r="H45" s="283" t="n"/>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="357" t="inlineStr">
         <is>
           <t>2CH
@@ -13603,19 +13603,19 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>Qui - CAl
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Ing - Vir
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-5º e 6º tempos</t>
-        </is>
-      </c>
       <c r="G9" s="183" t="inlineStr">
         <is>
           <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H9" s="183" t="n"/>
@@ -13771,13 +13771,13 @@
       <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Bio - Lza
-6º e 7º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
-6º e 7º tempos</t>
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -13847,19 +13847,19 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>AG10
@@ -13933,14 +13933,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14005,16 +14010,11 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-10º e 11º tempos</t>
-        </is>
-      </c>
+          <t>Fis - VSi
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
@@ -14085,8 +14085,8 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Fis - VSi
-6º e 7º tempos</t>
+          <t>Qui - CAl
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
@@ -14158,17 +14158,17 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="n"/>
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-7º tempo</t>
+          <t>Geo - Mlo
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H30" s="283" t="n"/>
@@ -14340,19 +14340,14 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
+          <t>Bio - Lza
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -14417,17 +14412,17 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>GL - EFr-Car-Swa
-3º e 4º tempos</t>
+          <t>Fil - LAn
+7º tempo</t>
         </is>
       </c>
       <c r="H39" s="283" t="n"/>
@@ -14478,13 +14473,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+      <c r="G42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14540,12 +14535,17 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="inlineStr">
         <is>
@@ -15302,21 +15302,21 @@
       <c r="E9" s="183" t="inlineStr">
         <is>
           <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F9" s="183" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-5º ao 7º tempos</t>
+          <t>Bio - Ale
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="J9" s="183" t="n"/>
@@ -15396,12 +15396,7 @@
         <f>B12+4</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="inlineStr">
         <is>
           <t>S3-11
@@ -15414,7 +15409,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -15480,17 +15480,17 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
           <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -15553,21 +15553,21 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Fis - Cadu
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+2º ao 4º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>Geo - Mar
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -15637,14 +15637,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl
+          <t>Mat - ClaMe/JJ
 1º e 2º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15707,21 +15712,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="362" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-9º tempo</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-5º ao 7º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -15789,11 +15789,16 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="n"/>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -15865,13 +15870,13 @@
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16039,17 +16044,17 @@
       </c>
       <c r="E36" s="283" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+2º ao 4º tempos</t>
+        </is>
+      </c>
+      <c r="F36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+9º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -16176,19 +16181,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-9º e 10º tempos</t>
-        </is>
-      </c>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -16245,18 +16245,18 @@
       <c r="E45" s="283" t="inlineStr">
         <is>
           <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-11º e 12º tempos</t>
-        </is>
-      </c>
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
-      <c r="I45" s="357" t="n"/>
+      <c r="I45" s="357" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
     </row>
@@ -16304,15 +16304,15 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-3º e 4º tempos</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="n"/>
       <c r="F48" s="360" t="n"/>
       <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="n"/>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16997,23 +16997,23 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
+          <t>Ing - PaH
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="inlineStr">
+        <is>
           <t>Geo - Mar
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H9" s="183" t="inlineStr">
         <is>
           <t>Fis - Cadu
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="n"/>
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -17094,8 +17094,8 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
+          <t>DaF - CBu-SGa-Swa
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -17113,7 +17113,7 @@
       <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Bio - Ale
-3º e 4º tempos</t>
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
@@ -17175,20 +17175,20 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
+          <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
           <t>Hist - Ver
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
-          <t>Mat - ClaMe/JJ
-10º e 11º tempos</t>
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="n"/>
@@ -17252,13 +17252,13 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
           <t>LP/LIT/RED - ACo/AMu/Raf
@@ -17331,14 +17331,19 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-10º e 11º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+5º e 6º tempos</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="n"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+11º tempo</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
@@ -17405,18 +17410,18 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Bio - Ale
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-4º ao 6º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="362" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
@@ -17486,13 +17491,18 @@
       <c r="E27" s="78" t="inlineStr">
         <is>
           <t>Ing - PaH
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -17560,17 +17570,12 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -17738,21 +17743,16 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>DaF - CBu-SGa-Swa
-6º e 7º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-4º tempo</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -17877,14 +17877,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+4º ao 6º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -17941,17 +17941,17 @@
       <c r="E45" s="283" t="inlineStr">
         <is>
           <t>Mat - ClaMe/JJ
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 3º e 4º tempos</t>
         </is>
       </c>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-8º e 9º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
       <c r="I45" s="357" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -18000,13 +18000,13 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="F48" s="360" t="n"/>
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="360" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G48" s="283" t="n"/>
       <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
@@ -18693,17 +18693,17 @@
       </c>
       <c r="E9" s="183" t="inlineStr">
         <is>
-          <t>Geo - Mar
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
 5º e 6º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
@@ -18790,19 +18790,19 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
+          <t>DaF - CBu-EFr-Eth
+3º e 4º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
           <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
 5º e 6º tempos</t>
         </is>
       </c>
@@ -18870,20 +18870,15 @@
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-5º e 6º tempos</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Hist - Wag
-11º e 12º tempos</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -18945,18 +18940,18 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
           <t>Mat - Bre/JJ
-3º e 4º tempos</t>
-        </is>
-      </c>
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -19025,7 +19020,7 @@
       <c r="E21" s="11" t="inlineStr">
         <is>
           <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
+3º e 4º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
@@ -19104,14 +19099,19 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-3º e 4º tempos</t>
-        </is>
-      </c>
-      <c r="G24" s="79" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F24" s="283" t="n"/>
+      <c r="G24" s="362" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
@@ -19179,13 +19179,13 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -19256,19 +19256,19 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-8º e 9º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Wag
+3º e 4º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19435,19 +19435,14 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
+      <c r="F36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 5º e 6º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-3º ao 5º tempos</t>
-        </is>
-      </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -19513,12 +19508,7 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-5º e 6º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
@@ -19526,7 +19516,12 @@
 10º tempo</t>
         </is>
       </c>
-      <c r="H39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+3º ao 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -19575,7 +19570,7 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
@@ -19634,11 +19629,16 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
+          <t>GL - CBu-EFr-Eth
+5º e 6º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>

--- a/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
@@ -5373,14 +5373,14 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
           <t>Hist - Wag
@@ -5470,13 +5470,18 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -5551,8 +5556,8 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -5614,12 +5619,7 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
@@ -5707,12 +5707,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -5776,12 +5771,7 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="inlineStr">
         <is>
@@ -5789,7 +5779,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -5864,12 +5859,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -5937,14 +5927,14 @@
       </c>
       <c r="E30" s="283" t="n"/>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -6117,14 +6107,14 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6190,15 +6180,20 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -6246,11 +6241,16 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Hist - Wag
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J42" s="265" t="n"/>
@@ -12029,7 +12029,12 @@
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -12101,12 +12106,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -12252,18 +12252,18 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -12329,12 +12329,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
@@ -12409,19 +12404,19 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -12488,14 +12483,14 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -12662,15 +12657,15 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12738,7 +12733,7 @@
       </c>
       <c r="E39" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
+          <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
@@ -12799,11 +12794,16 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -12858,14 +12858,14 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -13710,7 +13710,12 @@
         </is>
       </c>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
@@ -13782,12 +13787,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="183" t="n"/>
       <c r="L15" s="17" t="n"/>
       <c r="M15" s="15" t="n"/>
@@ -13933,18 +13933,18 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
@@ -14010,12 +14010,7 @@
       </c>
       <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
-      <c r="G24" s="353" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
       <c r="I24" s="78" t="inlineStr">
         <is>
@@ -14090,19 +14085,19 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>DaF - Eth-EFr-Swa
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -14169,14 +14164,14 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="n"/>
+      <c r="H30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -14343,15 +14338,20 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -14419,17 +14419,12 @@
       </c>
       <c r="E39" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
+          <t>Qui - CAl
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -14480,11 +14475,16 @@
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H42" s="283" t="n"/>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa/FBri
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -14539,14 +14539,14 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="n"/>
+      <c r="F45" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -18691,20 +18691,15 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="inlineStr">
         <is>
           <t>Hist - Wag
@@ -18794,13 +18789,18 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -18875,8 +18875,8 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -18938,14 +18938,14 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n"/>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Ing - PaH
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I18" s="350" t="inlineStr">
         <is>
           <t>LP/LIT/RED - AMu/Deb
@@ -19031,12 +19031,7 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -19100,12 +19095,7 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="inlineStr">
         <is>
@@ -19113,7 +19103,12 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -19188,12 +19183,7 @@
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -19266,14 +19256,14 @@
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
-      <c r="I30" s="283" t="n"/>
+      <c r="I30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J30" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -19446,14 +19436,14 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="G36" s="283" t="n"/>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -19519,15 +19509,20 @@
         <v/>
       </c>
       <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="n"/>
+      <c r="F39" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I39" s="283" t="n"/>
+      <c r="H39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -19575,11 +19570,16 @@
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
       <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="n"/>
+      <c r="H42" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I42" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Hist - Wag
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J42" s="265" t="n"/>

--- a/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
@@ -5367,26 +5367,11 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - Isb
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -5466,22 +5451,22 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
+          <t>Ing - Isb
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -5540,24 +5525,24 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -5619,13 +5604,18 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="350" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Hist - Wag
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -5694,7 +5684,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -5707,7 +5702,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -5771,7 +5771,12 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="inlineStr">
         <is>
@@ -5779,12 +5784,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -5850,16 +5850,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -5926,13 +5931,18 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J30" s="183" t="inlineStr">
@@ -6103,18 +6113,18 @@
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -6179,19 +6189,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Isb
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -6240,19 +6250,14 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -6307,17 +6312,12 @@
       </c>
       <c r="E45" s="283" t="inlineStr">
         <is>
-          <t>Ing - Isb
+          <t>DaF - CBu-EFr-Eth
 4º e 5º tempos</t>
         </is>
       </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
@@ -8588,20 +8588,10 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -8680,20 +8670,20 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -8754,14 +8744,14 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
+          <t>Redação - Raf
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -8827,17 +8817,17 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -8907,12 +8897,17 @@
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Port - Jana
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -8979,8 +8974,8 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Qui - Fab
-2º tempo</t>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="inlineStr">
@@ -9057,7 +9052,12 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
         <is>
@@ -9130,13 +9130,13 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -9306,20 +9306,15 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -9384,16 +9379,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -9508,7 +9508,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -9557,20 +9562,15 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="n"/>
       <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -10254,20 +10254,10 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Ing - APa-PaH-Velo
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -10346,20 +10336,20 @@
         <v/>
       </c>
       <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Ing - APa-PaH-Velo
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -10420,14 +10410,14 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>DaF - Caro-SGa-EFr
-1º e 2º tempos</t>
+          <t>Redação - Raf
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -10493,17 +10483,17 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Port - Jana
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mar
+6º e 7º tempos</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Caro-SGa-EFr
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -10573,12 +10563,17 @@
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-6º e 7º tempos</t>
+          <t>Port - Jana
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -10645,8 +10640,8 @@
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="353" t="inlineStr">
         <is>
-          <t>Qui - Fab
-2º tempo</t>
+          <t>Geo - Mar
+6º e 7º tempos</t>
         </is>
       </c>
       <c r="H24" s="283" t="inlineStr">
@@ -10723,7 +10718,12 @@
       </c>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Mat - BrSa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="inlineStr">
         <is>
@@ -10796,13 +10796,13 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Hist - JuLa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+2º tempo</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -10972,20 +10972,15 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Hist - JuLa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="inlineStr">
-        <is>
-          <t>GL - Caro-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -11050,16 +11045,21 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-2º tempo</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+3º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
-      <c r="I39" s="283" t="n"/>
+      <c r="I39" s="283" t="inlineStr">
+        <is>
+          <t>GL - Caro-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J39" s="265" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="4">
@@ -11174,7 +11174,12 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H45" s="283" t="n"/>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Redação - Raf
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -11223,20 +11228,15 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-1º tempo</t>
-        </is>
-      </c>
+      <c r="E48" s="283" t="n"/>
       <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="inlineStr">
-        <is>
-          <t>Redação - Raf
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Qui - Fab
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -11919,25 +11919,10 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -12018,20 +12003,20 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
           <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
 4º e 5º tempos</t>
         </is>
       </c>
@@ -12166,7 +12151,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
@@ -12175,16 +12165,11 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -12260,11 +12245,16 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12327,16 +12317,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -12404,18 +12399,18 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -12483,14 +12478,14 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
       <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -12659,13 +12654,13 @@
       </c>
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="n"/>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12731,14 +12726,14 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="inlineStr">
         <is>
           <t>Ing - APa
@@ -12792,19 +12787,19 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -12858,14 +12853,19 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -13600,25 +13600,10 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
       <c r="F9" s="183" t="n"/>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="H9" s="183" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
-        </is>
-      </c>
+      <c r="G9" s="183" t="n"/>
+      <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
@@ -13699,20 +13684,20 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
           <t>Mat - BrSa/FBri
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
 4º e 5º tempos</t>
         </is>
       </c>
@@ -13847,7 +13832,12 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+6º e 7º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
           <t>DaF - Eth-EFr-Swa
@@ -13856,16 +13846,11 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I18" s="350" t="n"/>
       <c r="J18" s="262" t="inlineStr">
         <is>
           <t>2CH 9,10,11,12</t>
@@ -13941,11 +13926,16 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
+          <t>Fis - VSi
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14008,16 +13998,21 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="n"/>
+      <c r="E24" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-5º tempo</t>
-        </is>
-      </c>
+      <c r="H24" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14085,18 +14080,18 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>DaF - Eth-EFr-Swa
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="n"/>
+      <c r="H27" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
@@ -14164,14 +14159,19 @@
         <v/>
       </c>
       <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="n"/>
-      <c r="H30" s="283" t="inlineStr">
-        <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G30" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Vir
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
         <is>
@@ -14342,16 +14342,11 @@
       <c r="F36" s="283" t="n"/>
       <c r="G36" s="283" t="inlineStr">
         <is>
-          <t>Ing - Vir
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="H36" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
+          <t>GL - EFr-Car-Swa
 2º e 3º tempos</t>
         </is>
       </c>
+      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -14417,14 +14412,14 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E39" s="283" t="n"/>
       <c r="F39" s="283" t="n"/>
-      <c r="G39" s="283" t="n"/>
+      <c r="G39" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
@@ -14473,19 +14468,19 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="inlineStr">
         <is>
           <t>Mat - BrSa/FBri
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="I42" s="283" t="n"/>
+      <c r="I42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+5º tempo</t>
+        </is>
+      </c>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -14539,14 +14534,19 @@
         <v/>
       </c>
       <c r="E45" s="283" t="n"/>
-      <c r="F45" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-6º e 7º tempos</t>
-        </is>
-      </c>
-      <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="n"/>
+      <c r="F45" s="283" t="n"/>
+      <c r="G45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H45" s="283" t="inlineStr">
+        <is>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -15299,24 +15299,9 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -15479,17 +15464,17 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
           <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Ing - Bea
@@ -15558,8 +15543,8 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
@@ -15635,21 +15620,26 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -15712,16 +15702,16 @@
         <f>B24+4</f>
         <v/>
       </c>
-      <c r="E24" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E24" s="283" t="n"/>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -15789,11 +15779,16 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -15862,14 +15857,14 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -16037,19 +16032,19 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -16129,7 +16124,12 @@
         </is>
       </c>
       <c r="G39" s="283" t="n"/>
-      <c r="H39" s="283" t="n"/>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - Bea
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -16176,19 +16176,14 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Ing - Bea
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="n"/>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
@@ -16242,20 +16237,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -16304,15 +16299,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+11º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -16995,24 +16995,9 @@
         <f>B9+4</f>
         <v/>
       </c>
-      <c r="E9" s="183" t="inlineStr">
-        <is>
-          <t>Qui - CAl
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G9" s="183" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="E9" s="183" t="n"/>
+      <c r="F9" s="183" t="n"/>
+      <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
       <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
@@ -17175,17 +17160,17 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="inlineStr">
-        <is>
           <t>Geo - Mar
-1º e 2º tempos</t>
-        </is>
-      </c>
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Ing - PaH
@@ -17254,8 +17239,8 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G18" s="11" t="n"/>
@@ -17331,21 +17316,26 @@
         <f>B21+4</f>
         <v/>
       </c>
-      <c r="E21" s="11" t="n"/>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="F21" s="62" t="inlineStr">
         <is>
-          <t>Mat - ClaMe/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="n"/>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-2º tempo</t>
-        </is>
-      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -17410,14 +17400,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>Ing - PaH
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="n"/>
-      <c r="I24" s="78" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+4º tempo</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -17485,11 +17480,16 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - ACo/AMu/Raf
-1º ao 3º tempos</t>
-        </is>
-      </c>
-      <c r="F27" s="283" t="n"/>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="F27" s="283" t="inlineStr">
+        <is>
+          <t>Hist - Ver
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="n"/>
       <c r="I27" s="283" t="n"/>
@@ -17560,17 +17560,12 @@
       </c>
       <c r="E30" s="283" t="inlineStr">
         <is>
-          <t>Ing - PaH
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - ACo/AMu/Raf
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F30" s="283" t="n"/>
-      <c r="G30" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-11º tempo</t>
-        </is>
-      </c>
+      <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
       <c r="J30" s="183" t="inlineStr">
@@ -17738,19 +17733,19 @@
         <f>B36+4</f>
         <v/>
       </c>
-      <c r="E36" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Hist - Ver
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="n"/>
+          <t>Mat - ClaMe/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="inlineStr">
+        <is>
+          <t>GL - CBu-Swa-SGa
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -17877,13 +17872,13 @@
         <v/>
       </c>
       <c r="E42" s="283" t="n"/>
-      <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="inlineStr">
-        <is>
-          <t>GL - CBu-Swa-SGa
+      <c r="F42" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-SGa-Swa
 4º e 5º tempos</t>
         </is>
       </c>
+      <c r="G42" s="283" t="n"/>
       <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
@@ -17938,20 +17933,20 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mar
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="inlineStr">
         <is>
-          <t>DaF - CBu-SGa-Swa
-4º e 5º tempos</t>
+          <t>Qui - CAl
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="G45" s="283" t="n"/>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="n"/>
       <c r="J45" s="269" t="n"/>
       <c r="L45" s="331" t="n"/>
@@ -18000,15 +17995,20 @@
         <f>B48+4</f>
         <v/>
       </c>
-      <c r="E48" s="283" t="inlineStr">
-        <is>
-          <t>Qui - CAl
+      <c r="E48" s="283" t="n"/>
+      <c r="F48" s="361" t="n"/>
+      <c r="G48" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+11º tempo</t>
+        </is>
+      </c>
+      <c r="H48" s="283" t="inlineStr">
+        <is>
+          <t>Fis - Cadu
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F48" s="361" t="n"/>
-      <c r="G48" s="283" t="n"/>
-      <c r="H48" s="283" t="n"/>
       <c r="I48" s="183" t="inlineStr">
         <is>
           <t>unterrichtsfrei sem aula</t>
@@ -18692,20 +18692,10 @@
         <v/>
       </c>
       <c r="E9" s="183" t="n"/>
-      <c r="F9" s="183" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
-1º e 2º tempos</t>
-        </is>
-      </c>
+      <c r="F9" s="183" t="n"/>
       <c r="G9" s="183" t="n"/>
       <c r="H9" s="183" t="n"/>
-      <c r="I9" s="183" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="I9" s="183" t="n"/>
       <c r="J9" s="183" t="n"/>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -18785,22 +18775,22 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>DaF - CBu-EFr-Eth
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
+          <t>Ing - PaH
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>GL - CBu-EFr-Eth
+9º e 10º tempos</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J12" s="183" t="n"/>
@@ -18859,24 +18849,24 @@
         <f>B15+4</f>
         <v/>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>Bio - Ale
+          <t>Fis - Cadu
 2º e 3º tempos</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>GL - CBu-EFr-Eth
-9º e 10º tempos</t>
-        </is>
-      </c>
+      <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-4º e 5º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J15" s="183" t="n"/>
@@ -18938,18 +18928,18 @@
           <t>unterrichtsfrei sem aula</t>
         </is>
       </c>
-      <c r="F18" s="11" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
+1º e 2º tempos</t>
+        </is>
+      </c>
       <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="350" t="inlineStr">
+        <is>
+          <t>Hist - Wag
 4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I18" s="350" t="inlineStr">
-        <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
         </is>
       </c>
       <c r="J18" s="262" t="inlineStr">
@@ -19018,7 +19008,12 @@
         <v/>
       </c>
       <c r="E21" s="11" t="n"/>
-      <c r="F21" s="62" t="n"/>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
           <t>S4-12
@@ -19031,7 +19026,12 @@
 2º ao 7º tempos</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -19095,7 +19095,12 @@
         <v/>
       </c>
       <c r="E24" s="283" t="n"/>
-      <c r="F24" s="283" t="n"/>
+      <c r="F24" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Ale
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="G24" s="79" t="n"/>
       <c r="H24" s="283" t="inlineStr">
         <is>
@@ -19103,12 +19108,7 @@
 9º e 10º tempos</t>
         </is>
       </c>
-      <c r="I24" s="78" t="inlineStr">
-        <is>
-          <t>Geo - Mar
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="I24" s="78" t="n"/>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -19174,16 +19174,21 @@
         <f>B27+4</f>
         <v/>
       </c>
-      <c r="E27" s="78" t="inlineStr">
-        <is>
-          <t>DaF - CBu-EFr-Eth
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="283" t="n"/>
+      <c r="G27" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+4º tempo</t>
+        </is>
+      </c>
+      <c r="H27" s="283" t="n"/>
+      <c r="I27" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl/Fab
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="F27" s="283" t="n"/>
-      <c r="G27" s="283" t="n"/>
-      <c r="H27" s="283" t="n"/>
-      <c r="I27" s="283" t="n"/>
       <c r="J27" s="265" t="n"/>
       <c r="L27" s="45" t="n"/>
       <c r="M27" s="323" t="inlineStr">
@@ -19249,19 +19254,19 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="inlineStr">
-        <is>
-          <t>Ing - PaH
+      <c r="E30" s="283" t="n"/>
+      <c r="F30" s="283" t="inlineStr">
+        <is>
+          <t>Mat - Bre/JJ
 1º e 2º tempos</t>
         </is>
       </c>
-      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - AMu/Deb
-1º ao 3º tempos</t>
+          <t>Geo - Mar
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="J30" s="183" t="inlineStr">
@@ -19432,18 +19437,18 @@
       <c r="E36" s="283" t="n"/>
       <c r="F36" s="283" t="inlineStr">
         <is>
-          <t>Bio - Ale
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>Fil - LAn
-4º tempo</t>
-        </is>
-      </c>
+          <t>Fis - Cadu
+1º e 2º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
-      <c r="I36" s="283" t="n"/>
+      <c r="I36" s="283" t="inlineStr">
+        <is>
+          <t>LP/LIT/RED - AMu/Deb
+1º ao 3º tempos</t>
+        </is>
+      </c>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
         <is>
@@ -19508,19 +19513,19 @@
         <f>B39+4</f>
         <v/>
       </c>
-      <c r="E39" s="283" t="n"/>
-      <c r="F39" s="283" t="inlineStr">
-        <is>
-          <t>Mat - Bre/JJ
+      <c r="E39" s="283" t="inlineStr">
+        <is>
+          <t>Ing - PaH
 1º e 2º tempos</t>
         </is>
       </c>
+      <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="n"/>
       <c r="H39" s="283" t="n"/>
       <c r="I39" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl/Fab
-2º e 3º tempos</t>
+          <t>Hist - Wag
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="J39" s="265" t="n"/>
@@ -19569,19 +19574,14 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Fis - Cadu
-2º e 3º tempos</t>
-        </is>
-      </c>
-      <c r="I42" s="283" t="inlineStr">
-        <is>
-          <t>Hist - Wag
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Soc - Kle
+2º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
+      <c r="I42" s="283" t="n"/>
       <c r="J42" s="265" t="n"/>
       <c r="L42" s="259" t="inlineStr">
         <is>
@@ -19634,14 +19634,14 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>DaF - CBu-EFr-Eth
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
-      <c r="G45" s="283" t="inlineStr">
-        <is>
-          <t>Soc - Kle
-6º tempo</t>
-        </is>
-      </c>
+      <c r="G45" s="283" t="n"/>
       <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>

--- a/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
+++ b/Horario desenvolvido/Proposta_1_Calendario_Provas_2026_2SEM.xlsx
@@ -12008,19 +12008,19 @@
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -12084,11 +12084,16 @@
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -12157,16 +12162,11 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -12237,24 +12237,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -12319,19 +12314,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -12399,16 +12394,16 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I27" s="283" t="n"/>
@@ -12477,13 +12472,13 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="n"/>
       <c r="H30" s="283" t="n"/>
       <c r="I30" s="283" t="n"/>
@@ -12653,14 +12648,19 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
+      <c r="H36" s="283" t="inlineStr">
+        <is>
+          <t>Ing - APa
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
       <c r="L36" s="81" t="inlineStr">
@@ -12730,14 +12730,14 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="H39" s="283" t="inlineStr">
         <is>
-          <t>Ing - APa
-2º e 3º tempos</t>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
         </is>
       </c>
       <c r="I39" s="283" t="n"/>
@@ -12787,13 +12787,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="inlineStr">
         <is>
           <t>Soc - Kle
@@ -12852,7 +12852,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
@@ -12860,12 +12865,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
@@ -13689,19 +13689,19 @@
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>DaF - Eth-EFr-Swa
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="L12" s="15" t="n"/>
       <c r="M12" s="15" t="n"/>
@@ -13765,11 +13765,16 @@
 4º e 5º tempos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
+          <t>Fis - VSi
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="I15" s="11" t="n"/>
@@ -13838,16 +13843,11 @@
 6º e 7º tempos</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>DaF - Eth-EFr-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="I18" s="350" t="n"/>
@@ -13918,24 +13918,19 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Mat - BrSa/FBri
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="F21" s="62" t="n"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>AG10
-2º ao 7º tempos</t>
-        </is>
-      </c>
+          <t>Hist - ALu
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="183" t="n"/>
       <c r="L21" s="80" t="inlineStr">
         <is>
@@ -14000,19 +13995,19 @@
       </c>
       <c r="E24" s="283" t="inlineStr">
         <is>
-          <t>Qui - CAl
-4º e 5º tempos</t>
+          <t>LP/LIT/RED - BPad/MFo/SMo
+1º ao 3º tempos</t>
         </is>
       </c>
       <c r="F24" s="283" t="n"/>
       <c r="G24" s="79" t="n"/>
-      <c r="H24" s="283" t="inlineStr">
-        <is>
-          <t>Geo - Mlo
-4º e 5º tempos</t>
-        </is>
-      </c>
-      <c r="I24" s="78" t="n"/>
+      <c r="H24" s="283" t="n"/>
+      <c r="I24" s="78" t="inlineStr">
+        <is>
+          <t>AG10
+2º ao 7º tempos</t>
+        </is>
+      </c>
       <c r="J24" s="265" t="n"/>
       <c r="L24" s="318" t="inlineStr">
         <is>
@@ -14080,16 +14075,16 @@
       </c>
       <c r="E27" s="78" t="inlineStr">
         <is>
-          <t>LP/LIT/RED - BPad/MFo/SMo
-1º ao 3º tempos</t>
+          <t>Mat - BrSa/FBri
+1º e 2º tempos</t>
         </is>
       </c>
       <c r="F27" s="283" t="n"/>
       <c r="G27" s="283" t="n"/>
       <c r="H27" s="283" t="inlineStr">
         <is>
-          <t>Fis - VSi
-1º e 2º tempos</t>
+          <t>Hist - ALu
+2º e 3º tempos</t>
         </is>
       </c>
       <c r="I27" s="283" t="n"/>
@@ -14158,13 +14153,13 @@
         <f>B30+4</f>
         <v/>
       </c>
-      <c r="E30" s="283" t="n"/>
-      <c r="F30" s="283" t="inlineStr">
-        <is>
-          <t>Bio - Lza
-10º e 11º tempos</t>
-        </is>
-      </c>
+      <c r="E30" s="283" t="inlineStr">
+        <is>
+          <t>Fis - VSi
+4º e 5º tempos</t>
+        </is>
+      </c>
+      <c r="F30" s="283" t="n"/>
       <c r="G30" s="283" t="inlineStr">
         <is>
           <t>Ing - Vir
@@ -14339,13 +14334,13 @@
         <v/>
       </c>
       <c r="E36" s="283" t="n"/>
-      <c r="F36" s="283" t="n"/>
-      <c r="G36" s="283" t="inlineStr">
-        <is>
-          <t>GL - EFr-Car-Swa
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="F36" s="283" t="inlineStr">
+        <is>
+          <t>Bio - Lza
+10º e 11º tempos</t>
+        </is>
+      </c>
+      <c r="G36" s="283" t="n"/>
       <c r="H36" s="283" t="n"/>
       <c r="I36" s="283" t="n"/>
       <c r="J36" s="265" t="n"/>
@@ -14416,11 +14411,16 @@
       <c r="F39" s="283" t="n"/>
       <c r="G39" s="283" t="inlineStr">
         <is>
-          <t>Fil - LAn
-1º tempo</t>
-        </is>
-      </c>
-      <c r="H39" s="283" t="n"/>
+          <t>GL - EFr-Car-Swa
+2º e 3º tempos</t>
+        </is>
+      </c>
+      <c r="H39" s="283" t="inlineStr">
+        <is>
+          <t>Geo - Mlo
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="I39" s="283" t="n"/>
       <c r="J39" s="265" t="n"/>
     </row>
@@ -14468,13 +14468,13 @@
       </c>
       <c r="E42" s="283" t="n"/>
       <c r="F42" s="283" t="n"/>
-      <c r="G42" s="283" t="n"/>
-      <c r="H42" s="283" t="inlineStr">
-        <is>
-          <t>Mat - BrSa/FBri
-4º e 5º tempos</t>
-        </is>
-      </c>
+      <c r="G42" s="283" t="inlineStr">
+        <is>
+          <t>Fil - LAn
+1º tempo</t>
+        </is>
+      </c>
+      <c r="H42" s="283" t="n"/>
       <c r="I42" s="283" t="inlineStr">
         <is>
           <t>Soc - Kle
@@ -14533,7 +14533,12 @@
         <f>B45+4</f>
         <v/>
       </c>
-      <c r="E45" s="283" t="n"/>
+      <c r="E45" s="283" t="inlineStr">
+        <is>
+          <t>Qui - CAl
+4º e 5º tempos</t>
+        </is>
+      </c>
       <c r="F45" s="283" t="n"/>
       <c r="G45" s="283" t="inlineStr">
         <is>
@@ -14541,12 +14546,7 @@
 2º e 3º tempos</t>
         </is>
       </c>
-      <c r="H45" s="283" t="inlineStr">
-        <is>
-          <t>Hist - ALu
-2º e 3º tempos</t>
-        </is>
-      </c>
+      <c r="H45" s="283" t="n"/>
       <c r="I45" s="358" t="inlineStr">
         <is>
           <t>2CH
